--- a/model performance comparison/Ratio_Cfree_Cnominal/Nicol_data/Fischer model_HepG2.xlsx
+++ b/model performance comparison/Ratio_Cfree_Cnominal/Nicol_data/Fischer model_HepG2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TAMU PHD\MassBalance project\Validation_Unilever\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TAMU PHD\MassBalance project\Paper writing\R1\model comparison_update_based reviewer\Validation_Unilever\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E105740-3A27-4B5C-BAAE-CFF4D5D3249C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A522DC97-F9FF-4CEF-9A95-B2612FE9E50F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Model structure" sheetId="1" r:id="rId1"/>
@@ -2038,6 +2038,143 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
@@ -2125,12 +2262,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2157,137 +2288,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -14092,8 +14092,8 @@
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
       <c r="F1" s="7"/>
-      <c r="G1" s="155"/>
-      <c r="H1" s="155"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="125"/>
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
       <c r="K1" s="7"/>
@@ -14126,19 +14126,19 @@
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
-      <c r="G2" s="155"/>
-      <c r="H2" s="155"/>
-      <c r="I2" s="100" t="s">
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="138" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="101"/>
-      <c r="M2" s="101"/>
-      <c r="N2" s="101"/>
-      <c r="O2" s="101"/>
-      <c r="P2" s="101"/>
-      <c r="Q2" s="102"/>
+      <c r="J2" s="139"/>
+      <c r="K2" s="139"/>
+      <c r="L2" s="139"/>
+      <c r="M2" s="139"/>
+      <c r="N2" s="139"/>
+      <c r="O2" s="139"/>
+      <c r="P2" s="139"/>
+      <c r="Q2" s="140"/>
       <c r="R2" s="7"/>
       <c r="S2" s="7"/>
       <c r="T2" s="7"/>
@@ -14162,17 +14162,17 @@
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
-      <c r="G3" s="155"/>
-      <c r="H3" s="155"/>
-      <c r="I3" s="103"/>
-      <c r="J3" s="104"/>
-      <c r="K3" s="104"/>
-      <c r="L3" s="104"/>
-      <c r="M3" s="104"/>
-      <c r="N3" s="104"/>
-      <c r="O3" s="104"/>
-      <c r="P3" s="104"/>
-      <c r="Q3" s="105"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="141"/>
+      <c r="J3" s="142"/>
+      <c r="K3" s="142"/>
+      <c r="L3" s="142"/>
+      <c r="M3" s="142"/>
+      <c r="N3" s="142"/>
+      <c r="O3" s="142"/>
+      <c r="P3" s="142"/>
+      <c r="Q3" s="143"/>
       <c r="R3" s="7"/>
       <c r="S3" s="7"/>
       <c r="T3" s="7"/>
@@ -14196,17 +14196,17 @@
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
-      <c r="G4" s="155"/>
-      <c r="H4" s="155"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="107"/>
-      <c r="K4" s="107"/>
-      <c r="L4" s="107"/>
-      <c r="M4" s="107"/>
-      <c r="N4" s="107"/>
-      <c r="O4" s="107"/>
-      <c r="P4" s="107"/>
-      <c r="Q4" s="108"/>
+      <c r="G4" s="125"/>
+      <c r="H4" s="125"/>
+      <c r="I4" s="144"/>
+      <c r="J4" s="145"/>
+      <c r="K4" s="145"/>
+      <c r="L4" s="145"/>
+      <c r="M4" s="145"/>
+      <c r="N4" s="145"/>
+      <c r="O4" s="145"/>
+      <c r="P4" s="145"/>
+      <c r="Q4" s="146"/>
       <c r="R4" s="7"/>
       <c r="S4" s="7"/>
       <c r="T4" s="7"/>
@@ -14230,19 +14230,19 @@
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
-      <c r="G5" s="155"/>
-      <c r="H5" s="155"/>
-      <c r="I5" s="109" t="s">
+      <c r="G5" s="125"/>
+      <c r="H5" s="125"/>
+      <c r="I5" s="147" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="110"/>
-      <c r="K5" s="110"/>
-      <c r="L5" s="110"/>
-      <c r="M5" s="110"/>
-      <c r="N5" s="110"/>
-      <c r="O5" s="110"/>
-      <c r="P5" s="110"/>
-      <c r="Q5" s="111"/>
+      <c r="J5" s="148"/>
+      <c r="K5" s="148"/>
+      <c r="L5" s="148"/>
+      <c r="M5" s="148"/>
+      <c r="N5" s="148"/>
+      <c r="O5" s="148"/>
+      <c r="P5" s="148"/>
+      <c r="Q5" s="149"/>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
       <c r="T5" s="7"/>
@@ -14266,8 +14266,8 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
-      <c r="G6" s="155"/>
-      <c r="H6" s="155"/>
+      <c r="G6" s="125"/>
+      <c r="H6" s="125"/>
       <c r="I6" s="50" t="s">
         <v>51</v>
       </c>
@@ -14277,14 +14277,14 @@
       <c r="K6" s="50" t="s">
         <v>48</v>
       </c>
-      <c r="L6" s="152" t="s">
+      <c r="L6" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="M6" s="153"/>
-      <c r="N6" s="153"/>
-      <c r="O6" s="153"/>
-      <c r="P6" s="153"/>
-      <c r="Q6" s="154"/>
+      <c r="M6" s="118"/>
+      <c r="N6" s="118"/>
+      <c r="O6" s="118"/>
+      <c r="P6" s="118"/>
+      <c r="Q6" s="119"/>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
       <c r="T6" s="7"/>
@@ -14308,8 +14308,8 @@
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
-      <c r="G7" s="155"/>
-      <c r="H7" s="155"/>
+      <c r="G7" s="125"/>
+      <c r="H7" s="125"/>
       <c r="I7" s="51" t="s">
         <v>21</v>
       </c>
@@ -14321,14 +14321,14 @@
         <f>J7/J7</f>
         <v>1</v>
       </c>
-      <c r="L7" s="146" t="s">
+      <c r="L7" s="100" t="s">
         <v>70</v>
       </c>
-      <c r="M7" s="147"/>
-      <c r="N7" s="147"/>
-      <c r="O7" s="147"/>
-      <c r="P7" s="147"/>
-      <c r="Q7" s="148"/>
+      <c r="M7" s="101"/>
+      <c r="N7" s="101"/>
+      <c r="O7" s="101"/>
+      <c r="P7" s="101"/>
+      <c r="Q7" s="102"/>
       <c r="R7" s="7"/>
       <c r="S7" s="7"/>
       <c r="T7" s="7"/>
@@ -14347,15 +14347,15 @@
     </row>
     <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="7"/>
-      <c r="B8" s="127" t="s">
+      <c r="B8" s="163" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="128"/>
-      <c r="D8" s="128"/>
-      <c r="E8" s="128"/>
-      <c r="F8" s="129"/>
-      <c r="G8" s="155"/>
-      <c r="H8" s="155"/>
+      <c r="C8" s="164"/>
+      <c r="D8" s="164"/>
+      <c r="E8" s="164"/>
+      <c r="F8" s="165"/>
+      <c r="G8" s="125"/>
+      <c r="H8" s="125"/>
       <c r="I8" s="52" t="s">
         <v>6</v>
       </c>
@@ -14367,14 +14367,14 @@
         <f>J8/J7</f>
         <v>0.99474841827768012</v>
       </c>
-      <c r="L8" s="146" t="s">
+      <c r="L8" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="M8" s="147"/>
-      <c r="N8" s="147"/>
-      <c r="O8" s="147"/>
-      <c r="P8" s="147"/>
-      <c r="Q8" s="148"/>
+      <c r="M8" s="101"/>
+      <c r="N8" s="101"/>
+      <c r="O8" s="101"/>
+      <c r="P8" s="101"/>
+      <c r="Q8" s="102"/>
       <c r="R8" s="7"/>
       <c r="S8" s="7"/>
       <c r="T8" s="7"/>
@@ -14393,13 +14393,13 @@
     </row>
     <row r="9" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="7"/>
-      <c r="B9" s="130"/>
-      <c r="C9" s="131"/>
-      <c r="D9" s="131"/>
-      <c r="E9" s="131"/>
-      <c r="F9" s="132"/>
-      <c r="G9" s="155"/>
-      <c r="H9" s="155"/>
+      <c r="B9" s="166"/>
+      <c r="C9" s="167"/>
+      <c r="D9" s="167"/>
+      <c r="E9" s="167"/>
+      <c r="F9" s="168"/>
+      <c r="G9" s="125"/>
+      <c r="H9" s="125"/>
       <c r="I9" s="51" t="s">
         <v>8</v>
       </c>
@@ -14411,14 +14411,14 @@
         <f>J9/J7</f>
         <v>5.0998242530755711E-3</v>
       </c>
-      <c r="L9" s="146" t="s">
+      <c r="L9" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="M9" s="147"/>
-      <c r="N9" s="147"/>
-      <c r="O9" s="147"/>
-      <c r="P9" s="147"/>
-      <c r="Q9" s="148"/>
+      <c r="M9" s="101"/>
+      <c r="N9" s="101"/>
+      <c r="O9" s="101"/>
+      <c r="P9" s="101"/>
+      <c r="Q9" s="102"/>
       <c r="R9" s="7"/>
       <c r="S9" s="7"/>
       <c r="T9" s="7"/>
@@ -14437,13 +14437,13 @@
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="7"/>
-      <c r="B10" s="133"/>
-      <c r="C10" s="134"/>
-      <c r="D10" s="134"/>
-      <c r="E10" s="134"/>
-      <c r="F10" s="135"/>
-      <c r="G10" s="155"/>
-      <c r="H10" s="155"/>
+      <c r="B10" s="169"/>
+      <c r="C10" s="170"/>
+      <c r="D10" s="170"/>
+      <c r="E10" s="170"/>
+      <c r="F10" s="171"/>
+      <c r="G10" s="125"/>
+      <c r="H10" s="125"/>
       <c r="I10" s="52" t="s">
         <v>9</v>
       </c>
@@ -14455,14 +14455,14 @@
         <f>J10/J7</f>
         <v>1.5175746924428823E-4</v>
       </c>
-      <c r="L10" s="146" t="s">
+      <c r="L10" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="M10" s="147"/>
-      <c r="N10" s="147"/>
-      <c r="O10" s="147"/>
-      <c r="P10" s="147"/>
-      <c r="Q10" s="148"/>
+      <c r="M10" s="101"/>
+      <c r="N10" s="101"/>
+      <c r="O10" s="101"/>
+      <c r="P10" s="101"/>
+      <c r="Q10" s="102"/>
       <c r="R10" s="7"/>
       <c r="S10" s="7"/>
       <c r="T10" s="7"/>
@@ -14481,24 +14481,24 @@
     </row>
     <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="7"/>
-      <c r="B11" s="136" t="s">
+      <c r="B11" s="128" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="137"/>
-      <c r="D11" s="137"/>
-      <c r="E11" s="137"/>
-      <c r="F11" s="138"/>
-      <c r="G11" s="155"/>
-      <c r="H11" s="155"/>
-      <c r="I11" s="171"/>
-      <c r="J11" s="171"/>
-      <c r="K11" s="171"/>
-      <c r="L11" s="171"/>
-      <c r="M11" s="171"/>
-      <c r="N11" s="171"/>
-      <c r="O11" s="171"/>
-      <c r="P11" s="171"/>
-      <c r="Q11" s="171"/>
+      <c r="C11" s="129"/>
+      <c r="D11" s="129"/>
+      <c r="E11" s="129"/>
+      <c r="F11" s="130"/>
+      <c r="G11" s="125"/>
+      <c r="H11" s="125"/>
+      <c r="I11" s="116"/>
+      <c r="J11" s="116"/>
+      <c r="K11" s="116"/>
+      <c r="L11" s="116"/>
+      <c r="M11" s="116"/>
+      <c r="N11" s="116"/>
+      <c r="O11" s="116"/>
+      <c r="P11" s="116"/>
+      <c r="Q11" s="116"/>
       <c r="R11" s="7"/>
       <c r="S11" s="7"/>
       <c r="T11" s="7"/>
@@ -14517,13 +14517,13 @@
     </row>
     <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="7"/>
-      <c r="B12" s="139"/>
-      <c r="C12" s="140"/>
-      <c r="D12" s="140"/>
-      <c r="E12" s="140"/>
-      <c r="F12" s="141"/>
-      <c r="G12" s="155"/>
-      <c r="H12" s="155"/>
+      <c r="B12" s="131"/>
+      <c r="C12" s="132"/>
+      <c r="D12" s="132"/>
+      <c r="E12" s="132"/>
+      <c r="F12" s="133"/>
+      <c r="G12" s="125"/>
+      <c r="H12" s="125"/>
       <c r="I12" s="50" t="s">
         <v>53</v>
       </c>
@@ -14533,14 +14533,14 @@
       <c r="K12" s="50" t="s">
         <v>48</v>
       </c>
-      <c r="L12" s="152" t="s">
+      <c r="L12" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="M12" s="153"/>
-      <c r="N12" s="153"/>
-      <c r="O12" s="153"/>
-      <c r="P12" s="153"/>
-      <c r="Q12" s="154"/>
+      <c r="M12" s="118"/>
+      <c r="N12" s="118"/>
+      <c r="O12" s="118"/>
+      <c r="P12" s="118"/>
+      <c r="Q12" s="119"/>
       <c r="R12" s="7"/>
       <c r="S12" s="7"/>
       <c r="T12" s="7"/>
@@ -14559,17 +14559,17 @@
     </row>
     <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="8"/>
-      <c r="B13" s="125" t="s">
+      <c r="B13" s="120" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="126"/>
-      <c r="D13" s="115" t="s">
+      <c r="C13" s="121"/>
+      <c r="D13" s="153" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="115"/>
-      <c r="F13" s="115"/>
-      <c r="G13" s="155"/>
-      <c r="H13" s="155"/>
+      <c r="E13" s="153"/>
+      <c r="F13" s="153"/>
+      <c r="G13" s="125"/>
+      <c r="H13" s="125"/>
       <c r="I13" s="51" t="s">
         <v>5</v>
       </c>
@@ -14581,14 +14581,14 @@
         <f>J13/J13</f>
         <v>1</v>
       </c>
-      <c r="L13" s="146" t="s">
+      <c r="L13" s="100" t="s">
         <v>73</v>
       </c>
-      <c r="M13" s="147"/>
-      <c r="N13" s="147"/>
-      <c r="O13" s="147"/>
-      <c r="P13" s="147"/>
-      <c r="Q13" s="148"/>
+      <c r="M13" s="101"/>
+      <c r="N13" s="101"/>
+      <c r="O13" s="101"/>
+      <c r="P13" s="101"/>
+      <c r="Q13" s="102"/>
       <c r="R13" s="7"/>
       <c r="S13" s="7"/>
       <c r="T13" s="7"/>
@@ -14613,13 +14613,13 @@
       <c r="C14" s="44">
         <v>300</v>
       </c>
-      <c r="D14" s="116" t="s">
+      <c r="D14" s="154" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="116"/>
-      <c r="F14" s="116"/>
-      <c r="G14" s="155"/>
-      <c r="H14" s="155"/>
+      <c r="E14" s="154"/>
+      <c r="F14" s="154"/>
+      <c r="G14" s="125"/>
+      <c r="H14" s="125"/>
       <c r="I14" s="52" t="s">
         <v>45</v>
       </c>
@@ -14631,14 +14631,14 @@
         <f>J14/J13</f>
         <v>0.99474841827768012</v>
       </c>
-      <c r="L14" s="149" t="s">
+      <c r="L14" s="122" t="s">
         <v>72</v>
       </c>
-      <c r="M14" s="150"/>
-      <c r="N14" s="150"/>
-      <c r="O14" s="150"/>
-      <c r="P14" s="150"/>
-      <c r="Q14" s="151"/>
+      <c r="M14" s="123"/>
+      <c r="N14" s="123"/>
+      <c r="O14" s="123"/>
+      <c r="P14" s="123"/>
+      <c r="Q14" s="124"/>
       <c r="R14" s="7"/>
       <c r="S14" s="7"/>
       <c r="T14" s="7"/>
@@ -14663,13 +14663,13 @@
       <c r="C15" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="117" t="s">
+      <c r="D15" s="155" t="s">
         <v>62</v>
       </c>
-      <c r="E15" s="117"/>
-      <c r="F15" s="117"/>
-      <c r="G15" s="155"/>
-      <c r="H15" s="155"/>
+      <c r="E15" s="155"/>
+      <c r="F15" s="155"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="125"/>
       <c r="I15" s="51" t="s">
         <v>46</v>
       </c>
@@ -14681,14 +14681,14 @@
         <f>J15/J13</f>
         <v>5.0998242530755711E-3</v>
       </c>
-      <c r="L15" s="146" t="s">
+      <c r="L15" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="M15" s="147"/>
-      <c r="N15" s="147"/>
-      <c r="O15" s="147"/>
-      <c r="P15" s="147"/>
-      <c r="Q15" s="148"/>
+      <c r="M15" s="101"/>
+      <c r="N15" s="101"/>
+      <c r="O15" s="101"/>
+      <c r="P15" s="101"/>
+      <c r="Q15" s="102"/>
       <c r="R15" s="7"/>
       <c r="S15" s="7"/>
       <c r="T15" s="7"/>
@@ -14714,13 +14714,13 @@
         <f>1-C18</f>
         <v>0.90333919156414766</v>
       </c>
-      <c r="D16" s="118" t="s">
+      <c r="D16" s="156" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="119"/>
-      <c r="F16" s="120"/>
-      <c r="G16" s="155"/>
-      <c r="H16" s="155"/>
+      <c r="E16" s="157"/>
+      <c r="F16" s="158"/>
+      <c r="G16" s="125"/>
+      <c r="H16" s="125"/>
       <c r="I16" s="52" t="s">
         <v>47</v>
       </c>
@@ -14732,14 +14732,14 @@
         <f>J16/J13</f>
         <v>1.5175746924428823E-4</v>
       </c>
-      <c r="L16" s="146" t="s">
+      <c r="L16" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="M16" s="147"/>
-      <c r="N16" s="147"/>
-      <c r="O16" s="147"/>
-      <c r="P16" s="147"/>
-      <c r="Q16" s="148"/>
+      <c r="M16" s="101"/>
+      <c r="N16" s="101"/>
+      <c r="O16" s="101"/>
+      <c r="P16" s="101"/>
+      <c r="Q16" s="102"/>
       <c r="R16" s="7"/>
       <c r="S16" s="7"/>
       <c r="T16" s="7"/>
@@ -14764,22 +14764,22 @@
       <c r="C17" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="D17" s="121" t="s">
+      <c r="D17" s="159" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="122"/>
-      <c r="F17" s="123"/>
-      <c r="G17" s="155"/>
-      <c r="H17" s="155"/>
-      <c r="I17" s="149"/>
-      <c r="J17" s="150"/>
-      <c r="K17" s="150"/>
-      <c r="L17" s="150"/>
-      <c r="M17" s="150"/>
-      <c r="N17" s="150"/>
-      <c r="O17" s="150"/>
-      <c r="P17" s="150"/>
-      <c r="Q17" s="151"/>
+      <c r="E17" s="160"/>
+      <c r="F17" s="161"/>
+      <c r="G17" s="125"/>
+      <c r="H17" s="125"/>
+      <c r="I17" s="122"/>
+      <c r="J17" s="123"/>
+      <c r="K17" s="123"/>
+      <c r="L17" s="123"/>
+      <c r="M17" s="123"/>
+      <c r="N17" s="123"/>
+      <c r="O17" s="123"/>
+      <c r="P17" s="123"/>
+      <c r="Q17" s="124"/>
       <c r="R17" s="7"/>
       <c r="S17" s="7"/>
       <c r="T17" s="7"/>
@@ -14804,13 +14804,13 @@
       <c r="C18" s="45">
         <v>9.6660808435852369E-2</v>
       </c>
-      <c r="D18" s="118" t="s">
+      <c r="D18" s="156" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="119"/>
-      <c r="F18" s="120"/>
-      <c r="G18" s="155"/>
-      <c r="H18" s="155"/>
+      <c r="E18" s="157"/>
+      <c r="F18" s="158"/>
+      <c r="G18" s="125"/>
+      <c r="H18" s="125"/>
       <c r="I18" s="50" t="s">
         <v>31</v>
       </c>
@@ -14820,14 +14820,14 @@
       <c r="K18" s="50" t="s">
         <v>48</v>
       </c>
-      <c r="L18" s="152" t="s">
+      <c r="L18" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="M18" s="153"/>
-      <c r="N18" s="153"/>
-      <c r="O18" s="153"/>
-      <c r="P18" s="153"/>
-      <c r="Q18" s="154"/>
+      <c r="M18" s="118"/>
+      <c r="N18" s="118"/>
+      <c r="O18" s="118"/>
+      <c r="P18" s="118"/>
+      <c r="Q18" s="119"/>
       <c r="R18" s="7"/>
       <c r="S18" s="7"/>
       <c r="T18" s="7"/>
@@ -14846,13 +14846,13 @@
     </row>
     <row r="19" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="7"/>
-      <c r="B19" s="117"/>
-      <c r="C19" s="117"/>
-      <c r="D19" s="117"/>
-      <c r="E19" s="117"/>
-      <c r="F19" s="117"/>
-      <c r="G19" s="155"/>
-      <c r="H19" s="155"/>
+      <c r="B19" s="155"/>
+      <c r="C19" s="155"/>
+      <c r="D19" s="155"/>
+      <c r="E19" s="155"/>
+      <c r="F19" s="155"/>
+      <c r="G19" s="125"/>
+      <c r="H19" s="125"/>
       <c r="I19" s="51" t="s">
         <v>5</v>
       </c>
@@ -14864,14 +14864,14 @@
         <f>J19/J19</f>
         <v>1</v>
       </c>
-      <c r="L19" s="146" t="s">
+      <c r="L19" s="100" t="s">
         <v>57</v>
       </c>
-      <c r="M19" s="147"/>
-      <c r="N19" s="147"/>
-      <c r="O19" s="147"/>
-      <c r="P19" s="147"/>
-      <c r="Q19" s="148"/>
+      <c r="M19" s="101"/>
+      <c r="N19" s="101"/>
+      <c r="O19" s="101"/>
+      <c r="P19" s="101"/>
+      <c r="Q19" s="102"/>
       <c r="R19" s="7"/>
       <c r="S19" s="7"/>
       <c r="T19" s="7"/>
@@ -14890,17 +14890,17 @@
     </row>
     <row r="20" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="7"/>
-      <c r="B20" s="125" t="s">
+      <c r="B20" s="120" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="126"/>
-      <c r="D20" s="115" t="s">
+      <c r="C20" s="121"/>
+      <c r="D20" s="153" t="s">
         <v>41</v>
       </c>
-      <c r="E20" s="115"/>
-      <c r="F20" s="115"/>
-      <c r="G20" s="155"/>
-      <c r="H20" s="155"/>
+      <c r="E20" s="153"/>
+      <c r="F20" s="153"/>
+      <c r="G20" s="125"/>
+      <c r="H20" s="125"/>
       <c r="I20" s="52" t="s">
         <v>45</v>
       </c>
@@ -14912,14 +14912,14 @@
         <f>J20/J19</f>
         <v>0.87354229684316542</v>
       </c>
-      <c r="L20" s="146" t="s">
+      <c r="L20" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="M20" s="147"/>
-      <c r="N20" s="147"/>
-      <c r="O20" s="147"/>
-      <c r="P20" s="147"/>
-      <c r="Q20" s="148"/>
+      <c r="M20" s="101"/>
+      <c r="N20" s="101"/>
+      <c r="O20" s="101"/>
+      <c r="P20" s="101"/>
+      <c r="Q20" s="102"/>
       <c r="R20" s="7"/>
       <c r="S20" s="7"/>
       <c r="T20" s="7"/>
@@ -14944,13 +14944,13 @@
       <c r="C21" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="D21" s="121" t="s">
+      <c r="D21" s="159" t="s">
         <v>63</v>
       </c>
-      <c r="E21" s="122"/>
-      <c r="F21" s="123"/>
-      <c r="G21" s="155"/>
-      <c r="H21" s="155"/>
+      <c r="E21" s="160"/>
+      <c r="F21" s="161"/>
+      <c r="G21" s="125"/>
+      <c r="H21" s="125"/>
       <c r="I21" s="51" t="s">
         <v>46</v>
       </c>
@@ -14962,14 +14962,14 @@
         <f>J21/J19</f>
         <v>9.4560212233021856E-2</v>
       </c>
-      <c r="L21" s="146" t="s">
+      <c r="L21" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="M21" s="147"/>
-      <c r="N21" s="147"/>
-      <c r="O21" s="147"/>
-      <c r="P21" s="147"/>
-      <c r="Q21" s="148"/>
+      <c r="M21" s="101"/>
+      <c r="N21" s="101"/>
+      <c r="O21" s="101"/>
+      <c r="P21" s="101"/>
+      <c r="Q21" s="102"/>
       <c r="R21" s="7"/>
       <c r="S21" s="7"/>
       <c r="T21" s="7"/>
@@ -14994,13 +14994,13 @@
       <c r="C22" s="46">
         <v>1.0000000000000001E-30</v>
       </c>
-      <c r="D22" s="124" t="s">
+      <c r="D22" s="162" t="s">
         <v>69</v>
       </c>
-      <c r="E22" s="124"/>
-      <c r="F22" s="124"/>
-      <c r="G22" s="155"/>
-      <c r="H22" s="155"/>
+      <c r="E22" s="162"/>
+      <c r="F22" s="162"/>
+      <c r="G22" s="125"/>
+      <c r="H22" s="125"/>
       <c r="I22" s="53" t="s">
         <v>47</v>
       </c>
@@ -15012,14 +15012,14 @@
         <f>J22/J19</f>
         <v>3.1897490923812694E-2</v>
       </c>
-      <c r="L22" s="146" t="s">
+      <c r="L22" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="M22" s="147"/>
-      <c r="N22" s="147"/>
-      <c r="O22" s="147"/>
-      <c r="P22" s="147"/>
-      <c r="Q22" s="148"/>
+      <c r="M22" s="101"/>
+      <c r="N22" s="101"/>
+      <c r="O22" s="101"/>
+      <c r="P22" s="101"/>
+      <c r="Q22" s="102"/>
       <c r="R22" s="7"/>
       <c r="S22" s="7"/>
       <c r="T22" s="7"/>
@@ -15038,22 +15038,22 @@
     </row>
     <row r="23" spans="1:32" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A23" s="7"/>
-      <c r="B23" s="112"/>
-      <c r="C23" s="113"/>
-      <c r="D23" s="113"/>
-      <c r="E23" s="113"/>
-      <c r="F23" s="114"/>
-      <c r="G23" s="155"/>
-      <c r="H23" s="155"/>
-      <c r="I23" s="166"/>
-      <c r="J23" s="167"/>
-      <c r="K23" s="167"/>
-      <c r="L23" s="167"/>
-      <c r="M23" s="167"/>
-      <c r="N23" s="167"/>
-      <c r="O23" s="167"/>
-      <c r="P23" s="167"/>
-      <c r="Q23" s="168"/>
+      <c r="B23" s="150"/>
+      <c r="C23" s="151"/>
+      <c r="D23" s="151"/>
+      <c r="E23" s="151"/>
+      <c r="F23" s="152"/>
+      <c r="G23" s="125"/>
+      <c r="H23" s="125"/>
+      <c r="I23" s="111"/>
+      <c r="J23" s="112"/>
+      <c r="K23" s="112"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="112"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="112"/>
+      <c r="Q23" s="113"/>
       <c r="R23" s="7"/>
       <c r="S23" s="7"/>
       <c r="T23" s="7"/>
@@ -15072,26 +15072,26 @@
     </row>
     <row r="24" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="7"/>
-      <c r="B24" s="136" t="s">
+      <c r="B24" s="128" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="137"/>
-      <c r="D24" s="137"/>
-      <c r="E24" s="137"/>
-      <c r="F24" s="138"/>
-      <c r="G24" s="155"/>
-      <c r="H24" s="155"/>
-      <c r="I24" s="160" t="s">
+      <c r="C24" s="129"/>
+      <c r="D24" s="129"/>
+      <c r="E24" s="129"/>
+      <c r="F24" s="130"/>
+      <c r="G24" s="125"/>
+      <c r="H24" s="125"/>
+      <c r="I24" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="J24" s="161"/>
-      <c r="K24" s="161"/>
-      <c r="L24" s="161"/>
-      <c r="M24" s="161"/>
-      <c r="N24" s="161"/>
-      <c r="O24" s="161"/>
-      <c r="P24" s="161"/>
-      <c r="Q24" s="162"/>
+      <c r="J24" s="106"/>
+      <c r="K24" s="106"/>
+      <c r="L24" s="106"/>
+      <c r="M24" s="106"/>
+      <c r="N24" s="106"/>
+      <c r="O24" s="106"/>
+      <c r="P24" s="106"/>
+      <c r="Q24" s="107"/>
       <c r="R24" s="7"/>
       <c r="S24" s="7"/>
       <c r="T24" s="7"/>
@@ -15110,22 +15110,22 @@
     </row>
     <row r="25" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="7"/>
-      <c r="B25" s="139"/>
-      <c r="C25" s="140"/>
-      <c r="D25" s="140"/>
-      <c r="E25" s="140"/>
-      <c r="F25" s="141"/>
-      <c r="G25" s="155"/>
-      <c r="H25" s="155"/>
-      <c r="I25" s="163"/>
-      <c r="J25" s="164"/>
-      <c r="K25" s="164"/>
-      <c r="L25" s="164"/>
-      <c r="M25" s="164"/>
-      <c r="N25" s="164"/>
-      <c r="O25" s="164"/>
-      <c r="P25" s="164"/>
-      <c r="Q25" s="165"/>
+      <c r="B25" s="131"/>
+      <c r="C25" s="132"/>
+      <c r="D25" s="132"/>
+      <c r="E25" s="132"/>
+      <c r="F25" s="133"/>
+      <c r="G25" s="125"/>
+      <c r="H25" s="125"/>
+      <c r="I25" s="108"/>
+      <c r="J25" s="109"/>
+      <c r="K25" s="109"/>
+      <c r="L25" s="109"/>
+      <c r="M25" s="109"/>
+      <c r="N25" s="109"/>
+      <c r="O25" s="109"/>
+      <c r="P25" s="109"/>
+      <c r="Q25" s="110"/>
       <c r="R25" s="7"/>
       <c r="S25" s="7"/>
       <c r="T25" s="7"/>
@@ -15144,48 +15144,48 @@
     </row>
     <row r="26" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="7"/>
-      <c r="B26" s="158" t="s">
+      <c r="B26" s="126" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="158" t="s">
+      <c r="C26" s="126" t="s">
         <v>12</v>
       </c>
-      <c r="D26" s="142" t="s">
+      <c r="D26" s="134" t="s">
         <v>49</v>
       </c>
-      <c r="E26" s="142" t="s">
+      <c r="E26" s="134" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="144" t="s">
+      <c r="F26" s="136" t="s">
         <v>68</v>
       </c>
-      <c r="G26" s="155"/>
-      <c r="H26" s="155"/>
-      <c r="I26" s="169" t="s">
+      <c r="G26" s="125"/>
+      <c r="H26" s="125"/>
+      <c r="I26" s="114" t="s">
         <v>55</v>
       </c>
-      <c r="J26" s="169" t="s">
+      <c r="J26" s="114" t="s">
         <v>56</v>
       </c>
-      <c r="K26" s="156" t="s">
+      <c r="K26" s="103" t="s">
         <v>76</v>
       </c>
-      <c r="L26" s="156" t="s">
+      <c r="L26" s="103" t="s">
         <v>54</v>
       </c>
-      <c r="M26" s="156" t="s">
+      <c r="M26" s="103" t="s">
         <v>61</v>
       </c>
-      <c r="N26" s="156" t="s">
+      <c r="N26" s="103" t="s">
         <v>64</v>
       </c>
-      <c r="O26" s="156" t="s">
+      <c r="O26" s="103" t="s">
         <v>75</v>
       </c>
-      <c r="P26" s="156" t="s">
+      <c r="P26" s="103" t="s">
         <v>66</v>
       </c>
-      <c r="Q26" s="156" t="s">
+      <c r="Q26" s="103" t="s">
         <v>67</v>
       </c>
       <c r="R26" s="9"/>
@@ -15206,22 +15206,22 @@
     </row>
     <row r="27" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="7"/>
-      <c r="B27" s="159"/>
-      <c r="C27" s="159"/>
-      <c r="D27" s="143"/>
-      <c r="E27" s="143"/>
-      <c r="F27" s="145"/>
-      <c r="G27" s="155"/>
-      <c r="H27" s="155"/>
-      <c r="I27" s="170"/>
-      <c r="J27" s="170"/>
-      <c r="K27" s="157"/>
-      <c r="L27" s="157"/>
-      <c r="M27" s="157"/>
-      <c r="N27" s="157"/>
-      <c r="O27" s="157"/>
-      <c r="P27" s="157"/>
-      <c r="Q27" s="157"/>
+      <c r="B27" s="127"/>
+      <c r="C27" s="127"/>
+      <c r="D27" s="135"/>
+      <c r="E27" s="135"/>
+      <c r="F27" s="137"/>
+      <c r="G27" s="125"/>
+      <c r="H27" s="125"/>
+      <c r="I27" s="115"/>
+      <c r="J27" s="115"/>
+      <c r="K27" s="104"/>
+      <c r="L27" s="104"/>
+      <c r="M27" s="104"/>
+      <c r="N27" s="104"/>
+      <c r="O27" s="104"/>
+      <c r="P27" s="104"/>
+      <c r="Q27" s="104"/>
       <c r="R27" s="7"/>
       <c r="S27" s="7"/>
       <c r="T27" s="7"/>
@@ -15247,31 +15247,31 @@
         <v>80</v>
       </c>
       <c r="D28" s="48">
-        <v>0.97789599999999988</v>
+        <v>-0.1223633442417989</v>
       </c>
       <c r="E28" s="48">
-        <v>1.067612</v>
+        <v>-0.65153095448481257</v>
       </c>
       <c r="F28" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G28" s="155"/>
-      <c r="H28" s="155"/>
+      <c r="G28" s="125"/>
+      <c r="H28" s="125"/>
       <c r="I28" s="55">
         <f t="shared" ref="I28:I47" si="1">IF(D28=0,"",LOG($K$15*10^D28+$K$16*10^E28+$K$14))</f>
-        <v>1.9111802855286381E-2</v>
+        <v>-5.9543910027850503E-4</v>
       </c>
       <c r="J28" s="55">
         <f t="shared" ref="J28:J47" si="2">IF(D28=0,"",LOG($K$21*10^D28+$K$22*10^E28+$K$20))</f>
-        <v>0.33141288274970654</v>
+        <v>-2.1363007670010294E-2</v>
       </c>
       <c r="K28" s="56">
         <f t="shared" ref="K28:K47" si="3">IF(D28=0,"",1/(1+10^D28*$J$15/$J$14+10^E28*$J$16/$J$14+10^J28*$J$19/$J$14))</f>
-        <v>0.95192219820843804</v>
+        <v>0.99611320267635428</v>
       </c>
       <c r="L28" s="56">
         <f t="shared" ref="L28:L47" si="4">IF(D28=0,"",1/(1+10^I28/10^J28*$J$13/$J$19))</f>
-        <v>2.0787003836832231E-38</v>
+        <v>9.6543546341963657E-39</v>
       </c>
       <c r="M28" s="56">
         <f t="shared" ref="M28:M47" si="5">IF(D28=0,"",1-L28)</f>
@@ -15279,23 +15279,23 @@
       </c>
       <c r="N28" s="56">
         <f t="shared" ref="N28:N47" si="6">IF(D28=0,"",1/(1/10^E28*$J$20/$J$22+10^D28/10^E28*$J$21/$J$22+10^I28/10^E28*$J$13/$J$22+1))</f>
-        <v>3.6119982896543085E-39</v>
+        <v>7.2162542031819394E-41</v>
       </c>
       <c r="O28" s="57">
         <f t="shared" ref="O28:O47" si="7">IF(D28=0,"",F28*K28*$J$7/$J$14)</f>
-        <v>9.5694768719171047E-6</v>
+        <v>1.0013719895137277E-5</v>
       </c>
       <c r="P28" s="57">
         <f t="shared" ref="P28:P47" si="8">IF(D28=0,"",O28*10^J28)</f>
-        <v>2.0525846647981087E-5</v>
+        <v>9.5330623048048989E-6</v>
       </c>
       <c r="Q28" s="57">
         <f t="shared" ref="Q28:Q47" si="9">IF(D28=0,"",F28*N28*$J$7/$J$22)</f>
-        <v>1.1181503321600376E-4</v>
+        <v>2.2339038911924274E-6</v>
       </c>
       <c r="R28" s="9">
         <f>O28/F28</f>
-        <v>0.95694768719171042</v>
+        <v>1.0013719895137276</v>
       </c>
       <c r="S28" s="11"/>
       <c r="T28" s="7"/>
@@ -15329,8 +15329,8 @@
       <c r="F29" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G29" s="155"/>
-      <c r="H29" s="155"/>
+      <c r="G29" s="125"/>
+      <c r="H29" s="125"/>
       <c r="I29" s="55">
         <f t="shared" si="1"/>
         <v>0.13164636702909191</v>
@@ -15368,7 +15368,7 @@
         <v>8.8654877279854577E-4</v>
       </c>
       <c r="R29" s="9">
-        <f t="shared" ref="R29:R54" si="10">O29/F29</f>
+        <f t="shared" ref="R29:R57" si="10">O29/F29</f>
         <v>0.738505328106699</v>
       </c>
       <c r="S29" s="7"/>
@@ -15394,50 +15394,57 @@
       <c r="C30" s="47" t="s">
         <v>84</v>
       </c>
-      <c r="D30" s="48"/>
-      <c r="E30" s="48"/>
+      <c r="D30" s="48">
+        <v>2.848199987724402</v>
+      </c>
+      <c r="E30" s="48">
+        <v>3.5741999825375301</v>
+      </c>
       <c r="F30" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G30" s="155"/>
-      <c r="H30" s="155"/>
-      <c r="I30" s="55" t="str">
+      <c r="G30" s="125"/>
+      <c r="H30" s="125"/>
+      <c r="I30" s="55">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J30" s="55" t="str">
+        <v>0.71260981758513819</v>
+      </c>
+      <c r="J30" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K30" s="86" t="str">
+        <v>2.2723110153039068</v>
+      </c>
+      <c r="K30" s="86">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L30" s="56" t="str">
+        <v>0.19279840631530765</v>
+      </c>
+      <c r="L30" s="56">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M30" s="56" t="str">
+        <v>3.6744472243375255E-37</v>
+      </c>
+      <c r="M30" s="56">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N30" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N30" s="56">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O30" s="57" t="str">
+        <v>2.3487538435783921E-37</v>
+      </c>
+      <c r="O30" s="57">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P30" s="57" t="str">
+        <v>1.9381624818174754E-6</v>
+      </c>
+      <c r="P30" s="57">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q30" s="57" t="str">
+        <v>3.6282833656485903E-4</v>
+      </c>
+      <c r="Q30" s="57">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R30" s="9"/>
+        <v>7.2709333719277423E-3</v>
+      </c>
+      <c r="R30" s="9">
+        <f t="shared" si="10"/>
+        <v>0.19381624818174753</v>
+      </c>
       <c r="S30" s="7"/>
       <c r="T30" s="7"/>
       <c r="U30" s="7"/>
@@ -15461,50 +15468,57 @@
       <c r="C31" s="47" t="s">
         <v>86</v>
       </c>
-      <c r="D31" s="48"/>
-      <c r="E31" s="48"/>
+      <c r="D31" s="48">
+        <v>-0.98996462433878363</v>
+      </c>
+      <c r="E31" s="48">
+        <v>-1.885724324763622</v>
+      </c>
       <c r="F31" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G31" s="155"/>
-      <c r="H31" s="155"/>
-      <c r="I31" s="55" t="str">
+      <c r="G31" s="125"/>
+      <c r="H31" s="125"/>
+      <c r="I31" s="55">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J31" s="55" t="str">
+        <v>-2.0580843529421572E-3</v>
+      </c>
+      <c r="J31" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K31" s="56" t="str">
+        <v>-5.3727409846454792E-2</v>
+      </c>
+      <c r="K31" s="56">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L31" s="56" t="str">
+        <v>0.99947363318430105</v>
+      </c>
+      <c r="L31" s="56">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M31" s="56" t="str">
+        <v>8.9912793470842175E-39</v>
+      </c>
+      <c r="M31" s="56">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N31" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N31" s="56">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O31" s="57" t="str">
+        <v>4.2226112306732045E-42</v>
+      </c>
+      <c r="O31" s="57">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P31" s="57" t="str">
+        <v>1.0047501607640677E-5</v>
+      </c>
+      <c r="P31" s="57">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q31" s="57" t="str">
+        <v>8.8783175534129614E-6</v>
+      </c>
+      <c r="Q31" s="57">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R31" s="9"/>
+        <v>1.3071750791476229E-7</v>
+      </c>
+      <c r="R31" s="9">
+        <f t="shared" si="10"/>
+        <v>1.0047501607640676</v>
+      </c>
       <c r="S31" s="7"/>
       <c r="T31" s="7"/>
       <c r="U31" s="7"/>
@@ -15537,8 +15551,8 @@
       <c r="F32" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G32" s="155"/>
-      <c r="H32" s="155"/>
+      <c r="G32" s="125"/>
+      <c r="H32" s="125"/>
       <c r="I32" s="55">
         <f t="shared" si="1"/>
         <v>1.188756138930017</v>
@@ -15602,50 +15616,57 @@
       <c r="C33" s="47" t="s">
         <v>90</v>
       </c>
-      <c r="D33" s="48"/>
-      <c r="E33" s="48"/>
+      <c r="D33" s="48">
+        <v>-7.2373500000194575</v>
+      </c>
+      <c r="E33" s="48">
+        <v>-10.772850000027681</v>
+      </c>
       <c r="F33" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G33" s="155"/>
-      <c r="H33" s="155"/>
-      <c r="I33" s="55" t="str">
+      <c r="G33" s="125"/>
+      <c r="H33" s="125"/>
+      <c r="I33" s="55">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J33" s="55" t="str">
+        <v>-2.2867426119237313E-3</v>
+      </c>
+      <c r="J33" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K33" s="56" t="str">
+        <v>-5.8716058948248731E-2</v>
+      </c>
+      <c r="K33" s="56">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L33" s="56" t="str">
+        <v>0.9999999997031781</v>
+      </c>
+      <c r="L33" s="56">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M33" s="56" t="str">
+        <v>8.8932704560683238E-39</v>
+      </c>
+      <c r="M33" s="56">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N33" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N33" s="56">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O33" s="57" t="str">
+        <v>5.4787827717507093E-51</v>
+      </c>
+      <c r="O33" s="57">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P33" s="57" t="str">
+        <v>1.0052793061330932E-5</v>
+      </c>
+      <c r="P33" s="57">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q33" s="57" t="str">
+        <v>8.7815399955252553E-6</v>
+      </c>
+      <c r="Q33" s="57">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R33" s="9"/>
+        <v>1.6960425462028815E-16</v>
+      </c>
+      <c r="R33" s="9">
+        <f t="shared" si="10"/>
+        <v>1.0052793061330931</v>
+      </c>
       <c r="S33" s="7"/>
       <c r="T33" s="7"/>
       <c r="U33" s="7"/>
@@ -15669,50 +15690,57 @@
       <c r="C34" s="47" t="s">
         <v>92</v>
       </c>
-      <c r="D34" s="48"/>
-      <c r="E34" s="48"/>
+      <c r="D34" s="48">
+        <v>0.89837073464087869</v>
+      </c>
+      <c r="E34" s="48">
+        <v>0.80049921406660218</v>
+      </c>
       <c r="F34" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G34" s="155"/>
-      <c r="H34" s="155"/>
-      <c r="I34" s="55" t="str">
+      <c r="G34" s="125"/>
+      <c r="H34" s="125"/>
+      <c r="I34" s="55">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J34" s="55" t="str">
+        <v>1.5386877609496322E-2</v>
+      </c>
+      <c r="J34" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K34" s="56" t="str">
+        <v>0.26086747897772927</v>
+      </c>
+      <c r="K34" s="56">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L34" s="56" t="str">
+        <v>0.96012190831163979</v>
+      </c>
+      <c r="L34" s="56">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M34" s="56" t="str">
+        <v>1.7822614672490652E-38</v>
+      </c>
+      <c r="M34" s="56">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N34" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N34" s="56">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O34" s="57" t="str">
+        <v>1.9695167347418257E-39</v>
+      </c>
+      <c r="O34" s="57">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P34" s="57" t="str">
+        <v>9.6519068607719636E-6</v>
+      </c>
+      <c r="P34" s="57">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q34" s="57" t="str">
+        <v>1.7598700539295681E-5</v>
+      </c>
+      <c r="Q34" s="57">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R34" s="9"/>
+        <v>6.096945830384353E-5</v>
+      </c>
+      <c r="R34" s="9">
+        <f t="shared" si="10"/>
+        <v>0.96519068607719627</v>
+      </c>
       <c r="S34" s="7"/>
       <c r="T34" s="7"/>
       <c r="U34" s="7"/>
@@ -15736,50 +15764,57 @@
       <c r="C35" s="47" t="s">
         <v>94</v>
       </c>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
+      <c r="D35" s="48">
+        <v>5.1201999877244022</v>
+      </c>
+      <c r="E35" s="48">
+        <v>6.8061999825375299</v>
+      </c>
       <c r="F35" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G35" s="155"/>
-      <c r="H35" s="155"/>
-      <c r="I35" s="55" t="str">
+      <c r="G35" s="125"/>
+      <c r="H35" s="125"/>
+      <c r="I35" s="55">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J35" s="55" t="str">
+        <v>3.2161354663663526</v>
+      </c>
+      <c r="J35" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K35" s="56" t="str">
+        <v>5.3357094299621073</v>
+      </c>
+      <c r="K35" s="56">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L35" s="56" t="str">
+        <v>6.0475266503206301E-4</v>
+      </c>
+      <c r="L35" s="56">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M35" s="56" t="str">
+        <v>1.3337203567472012E-36</v>
+      </c>
+      <c r="M35" s="56">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N35" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N35" s="56">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O35" s="57" t="str">
+        <v>1.2569322084526718E-36</v>
+      </c>
+      <c r="O35" s="57">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P35" s="57" t="str">
+        <v>6.0794533966602276E-9</v>
+      </c>
+      <c r="P35" s="57">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q35" s="57" t="str">
+        <v>1.3169641824656315E-3</v>
+      </c>
+      <c r="Q35" s="57">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R35" s="9"/>
+        <v>3.8910294348963113E-2</v>
+      </c>
+      <c r="R35" s="9">
+        <f t="shared" si="10"/>
+        <v>6.0794533966602267E-4</v>
+      </c>
       <c r="S35" s="7"/>
       <c r="T35" s="7"/>
       <c r="U35" s="7"/>
@@ -15812,8 +15847,8 @@
       <c r="F36" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G36" s="155"/>
-      <c r="H36" s="155"/>
+      <c r="G36" s="125"/>
+      <c r="H36" s="125"/>
       <c r="I36" s="55">
         <f t="shared" si="1"/>
         <v>9.0992645106186959E-2</v>
@@ -15886,8 +15921,8 @@
       <c r="F37" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G37" s="155"/>
-      <c r="H37" s="155"/>
+      <c r="G37" s="125"/>
+      <c r="H37" s="125"/>
       <c r="I37" s="55">
         <f t="shared" si="1"/>
         <v>0.17604780001944342</v>
@@ -15960,8 +15995,8 @@
       <c r="F38" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G38" s="155"/>
-      <c r="H38" s="155"/>
+      <c r="G38" s="125"/>
+      <c r="H38" s="125"/>
       <c r="I38" s="55">
         <f t="shared" si="1"/>
         <v>6.1269165998999722E-3</v>
@@ -16025,50 +16060,57 @@
       <c r="C39" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="D39" s="48"/>
-      <c r="E39" s="48"/>
+      <c r="D39" s="48">
+        <v>4.3320999877244022</v>
+      </c>
+      <c r="E39" s="48">
+        <v>5.6850999825375297</v>
+      </c>
       <c r="F39" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G39" s="155"/>
-      <c r="H39" s="155"/>
-      <c r="I39" s="55" t="str">
+      <c r="G39" s="125"/>
+      <c r="H39" s="125"/>
+      <c r="I39" s="55">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J39" s="55" t="str">
+        <v>2.2649340284107091</v>
+      </c>
+      <c r="J39" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K39" s="56" t="str">
+        <v>4.2425358088051919</v>
+      </c>
+      <c r="K39" s="56">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L39" s="56" t="str">
+        <v>5.4047950339141705E-3</v>
+      </c>
+      <c r="L39" s="56">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M39" s="56" t="str">
+        <v>9.6181732734107031E-37</v>
+      </c>
+      <c r="M39" s="56">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N39" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N39" s="56">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O39" s="57" t="str">
+        <v>8.4998897569395189E-37</v>
+      </c>
+      <c r="O39" s="57">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P39" s="57" t="str">
+        <v>5.4333286030975558E-8</v>
+      </c>
+      <c r="P39" s="57">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q39" s="57" t="str">
+        <v>9.4973355079643778E-4</v>
+      </c>
+      <c r="Q39" s="57">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R39" s="9"/>
+        <v>2.6312732711607216E-2</v>
+      </c>
+      <c r="R39" s="9">
+        <f t="shared" si="10"/>
+        <v>5.4333286030975557E-3</v>
+      </c>
       <c r="S39" s="7"/>
       <c r="T39" s="7"/>
       <c r="U39" s="7"/>
@@ -16092,50 +16134,57 @@
       <c r="C40" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="D40" s="48"/>
-      <c r="E40" s="48"/>
+      <c r="D40" s="48">
+        <v>2.713299987724402</v>
+      </c>
+      <c r="E40" s="48">
+        <v>3.3822999825375302</v>
+      </c>
       <c r="F40" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G40" s="155"/>
-      <c r="H40" s="155"/>
-      <c r="I40" s="55" t="str">
+      <c r="G40" s="125"/>
+      <c r="H40" s="125"/>
+      <c r="I40" s="55">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J40" s="55" t="str">
+        <v>0.60164447667090892</v>
+      </c>
+      <c r="J40" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K40" s="56" t="str">
+        <v>2.1026490087304119</v>
+      </c>
+      <c r="K40" s="56">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L40" s="56" t="str">
+        <v>0.24892515176882185</v>
+      </c>
+      <c r="L40" s="56">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M40" s="56" t="str">
+        <v>3.2099284232795837E-37</v>
+      </c>
+      <c r="M40" s="56">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N40" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N40" s="56">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O40" s="57" t="str">
+        <v>1.9494084521127915E-37</v>
+      </c>
+      <c r="O40" s="57">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P40" s="57" t="str">
+        <v>2.5023930392351264E-6</v>
+      </c>
+      <c r="P40" s="57">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q40" s="57" t="str">
+        <v>3.1696005390872636E-4</v>
+      </c>
+      <c r="Q40" s="57">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R40" s="9"/>
+        <v>6.0346975093781589E-3</v>
+      </c>
+      <c r="R40" s="9">
+        <f t="shared" si="10"/>
+        <v>0.25023930392351262</v>
+      </c>
       <c r="S40" s="7"/>
       <c r="T40" s="7"/>
       <c r="U40" s="7"/>
@@ -16168,8 +16217,8 @@
       <c r="F41" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G41" s="155"/>
-      <c r="H41" s="155"/>
+      <c r="G41" s="125"/>
+      <c r="H41" s="125"/>
       <c r="I41" s="55">
         <f t="shared" si="1"/>
         <v>1.3866457069131444</v>
@@ -16234,31 +16283,31 @@
         <v>108</v>
       </c>
       <c r="D42" s="48">
-        <v>2.0168880000000002</v>
+        <v>-1.2627122753537208</v>
       </c>
       <c r="E42" s="48">
-        <v>2.2161360000000005</v>
+        <v>-2.2737174621228986</v>
       </c>
       <c r="F42" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G42" s="155"/>
-      <c r="H42" s="155"/>
+      <c r="G42" s="125"/>
+      <c r="H42" s="125"/>
       <c r="I42" s="55">
         <f t="shared" si="1"/>
-        <v>0.19030789810251308</v>
+        <v>-2.1648125628206212E-3</v>
       </c>
       <c r="J42" s="55">
         <f t="shared" si="2"/>
-        <v>1.2027958056790993</v>
+        <v>-5.6072269123615688E-2</v>
       </c>
       <c r="K42" s="56">
         <f t="shared" si="3"/>
-        <v>0.6418083442949708</v>
+        <v>0.99971928479761296</v>
       </c>
       <c r="L42" s="56">
         <f t="shared" si="4"/>
-        <v>1.0422663674731322E-37</v>
+        <v>8.9450620960670439E-39</v>
       </c>
       <c r="M42" s="56">
         <f t="shared" si="5"/>
@@ -16266,23 +16315,23 @@
       </c>
       <c r="N42" s="56">
         <f t="shared" si="6"/>
-        <v>3.4282733347920266E-38</v>
+        <v>1.7286007189384254E-42</v>
       </c>
       <c r="O42" s="57">
         <f t="shared" si="7"/>
-        <v>6.4519664721478612E-6</v>
+        <v>1.0049971092475218E-5</v>
       </c>
       <c r="P42" s="57">
         <f t="shared" si="8"/>
-        <v>1.029171870704864E-4</v>
+        <v>8.8326809520866605E-6</v>
       </c>
       <c r="Q42" s="57">
         <f t="shared" si="9"/>
-        <v>1.0612754106259497E-3</v>
+        <v>5.3511527776444902E-8</v>
       </c>
       <c r="R42" s="9">
         <f t="shared" si="10"/>
-        <v>0.64519664721478609</v>
+        <v>1.0049971092475216</v>
       </c>
       <c r="S42" s="7"/>
       <c r="T42" s="7"/>
@@ -16308,31 +16357,31 @@
         <v>110</v>
       </c>
       <c r="D43" s="48">
-        <v>4.2132720000000008</v>
+        <v>2.1582748772295566</v>
       </c>
       <c r="E43" s="48">
-        <v>4.705258999999999</v>
+        <v>2.5927572197209185</v>
       </c>
       <c r="F43" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G43" s="155"/>
-      <c r="H43" s="155"/>
+      <c r="G43" s="125"/>
+      <c r="H43" s="125"/>
       <c r="I43" s="55">
         <f t="shared" si="1"/>
-        <v>1.9639211957971754</v>
+        <v>0.25246259798372345</v>
       </c>
       <c r="J43" s="55">
         <f t="shared" si="2"/>
-        <v>3.5002634119487781</v>
+        <v>1.4309786108559837</v>
       </c>
       <c r="K43" s="56">
         <f t="shared" si="3"/>
-        <v>1.0809162887927371E-2</v>
+        <v>0.55622519797691783</v>
       </c>
       <c r="L43" s="56">
         <f t="shared" si="4"/>
-        <v>3.4820342007723223E-37</v>
+        <v>1.5275900790921898E-37</v>
       </c>
       <c r="M43" s="56">
         <f t="shared" si="5"/>
@@ -16340,23 +16389,23 @@
       </c>
       <c r="N43" s="56">
         <f t="shared" si="6"/>
-        <v>1.7806769747994794E-37</v>
+        <v>7.0719952545981828E-38</v>
       </c>
       <c r="O43" s="57">
         <f t="shared" si="7"/>
-        <v>1.0866227771080543E-7</v>
+        <v>5.5916168124194968E-6</v>
       </c>
       <c r="P43" s="57">
         <f t="shared" si="8"/>
-        <v>3.4382877200146695E-4</v>
+        <v>1.508398225667612E-4</v>
       </c>
       <c r="Q43" s="57">
         <f t="shared" si="9"/>
-        <v>5.5123629392203471E-3</v>
+        <v>2.1892462866365237E-3</v>
       </c>
       <c r="R43" s="9">
         <f t="shared" si="10"/>
-        <v>1.0866227771080542E-2</v>
+        <v>0.55916168124194965</v>
       </c>
       <c r="S43" s="7"/>
       <c r="T43" s="7"/>
@@ -16381,50 +16430,57 @@
       <c r="C44" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="D44" s="48"/>
-      <c r="E44" s="48"/>
+      <c r="D44" s="48">
+        <v>0.51229998772440222</v>
+      </c>
+      <c r="E44" s="48">
+        <v>0.25129998253752994</v>
+      </c>
       <c r="F44" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G44" s="155"/>
-      <c r="H44" s="155"/>
-      <c r="I44" s="55" t="str">
+      <c r="G44" s="125"/>
+      <c r="H44" s="125"/>
+      <c r="I44" s="55">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J44" s="55" t="str">
+        <v>5.0128695514360909E-3</v>
+      </c>
+      <c r="J44" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K44" s="56" t="str">
+        <v>9.2738409446529238E-2</v>
+      </c>
+      <c r="K44" s="56">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L44" s="56" t="str">
+        <v>0.98333248753680669</v>
+      </c>
+      <c r="L44" s="56">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M44" s="56" t="str">
+        <v>1.239413882223258E-38</v>
+      </c>
+      <c r="M44" s="56">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N44" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N44" s="56">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O44" s="57" t="str">
+        <v>5.6955340403099668E-40</v>
+      </c>
+      <c r="O44" s="57">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P44" s="57" t="str">
+        <v>9.8852380106254494E-6</v>
+      </c>
+      <c r="P44" s="57">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q44" s="57" t="str">
+        <v>1.2238425258197446E-5</v>
+      </c>
+      <c r="Q44" s="57">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R44" s="9"/>
+        <v>1.7631412775698998E-5</v>
+      </c>
+      <c r="R44" s="9">
+        <f t="shared" si="10"/>
+        <v>0.98852380106254489</v>
+      </c>
       <c r="S44" s="7"/>
       <c r="T44" s="7"/>
       <c r="U44" s="7"/>
@@ -16448,50 +16504,57 @@
       <c r="C45" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="D45" s="48"/>
-      <c r="E45" s="48"/>
+      <c r="D45" s="48">
+        <v>0.92271245461153151</v>
+      </c>
+      <c r="E45" s="48">
+        <v>0.83512616782767168</v>
+      </c>
       <c r="F45" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G45" s="155"/>
-      <c r="H45" s="155"/>
-      <c r="I45" s="55" t="str">
+      <c r="G45" s="125"/>
+      <c r="H45" s="125"/>
+      <c r="I45" s="55">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J45" s="55" t="str">
+        <v>1.6394313607087763E-2</v>
+      </c>
+      <c r="J45" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K45" s="56" t="str">
+        <v>0.2748968182073846</v>
+      </c>
+      <c r="K45" s="56">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L45" s="56" t="str">
+        <v>0.9578972879256985</v>
+      </c>
+      <c r="L45" s="56">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M45" s="56" t="str">
+        <v>1.8365100991682406E-38</v>
+      </c>
+      <c r="M45" s="56">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N45" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N45" s="56">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O45" s="57" t="str">
+        <v>2.1280370898705404E-39</v>
+      </c>
+      <c r="O45" s="57">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P45" s="57" t="str">
+        <v>9.6295432123854385E-6</v>
+      </c>
+      <c r="P45" s="57">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q45" s="57" t="str">
+        <v>1.8134371340328952E-5</v>
+      </c>
+      <c r="Q45" s="57">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R45" s="9"/>
+        <v>6.5876702813039121E-5</v>
+      </c>
+      <c r="R45" s="9">
+        <f t="shared" si="10"/>
+        <v>0.96295432123854374</v>
+      </c>
       <c r="S45" s="7"/>
       <c r="T45" s="7"/>
       <c r="U45" s="7"/>
@@ -16516,31 +16579,31 @@
         <v>116</v>
       </c>
       <c r="D46" s="48">
-        <v>2.9091840000000002</v>
+        <v>1.6452318246143236</v>
       </c>
       <c r="E46" s="48">
-        <v>3.4102429999999995</v>
+        <v>1.8629354124795308</v>
       </c>
       <c r="F46" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G46" s="155"/>
-      <c r="H46" s="155"/>
+      <c r="G46" s="125"/>
+      <c r="H46" s="125"/>
       <c r="I46" s="55">
         <f t="shared" si="1"/>
-        <v>0.74214004662509647</v>
+        <v>9.0303999495995046E-2</v>
       </c>
       <c r="J46" s="55">
         <f t="shared" si="2"/>
-        <v>2.2031029578389063</v>
+        <v>0.86792168019773652</v>
       </c>
       <c r="K46" s="56">
         <f t="shared" si="3"/>
-        <v>0.18012467517062158</v>
+        <v>0.80799608738038742</v>
       </c>
       <c r="L46" s="56">
         <f t="shared" si="4"/>
-        <v>2.9272089714956586E-37</v>
+        <v>6.068879255931269E-38</v>
       </c>
       <c r="M46" s="56">
         <f t="shared" si="5"/>
@@ -16548,23 +16611,23 @@
       </c>
       <c r="N46" s="56">
         <f t="shared" si="6"/>
-        <v>1.504354855893811E-37</v>
+        <v>1.9137215695704943E-38</v>
       </c>
       <c r="O46" s="57">
         <f t="shared" si="7"/>
-        <v>1.8107560852671846E-6</v>
+        <v>8.1226174632110707E-6</v>
       </c>
       <c r="P46" s="57">
         <f t="shared" si="8"/>
-        <v>2.890433028595166E-4</v>
+        <v>5.9926329888695525E-5</v>
       </c>
       <c r="Q46" s="57">
         <f t="shared" si="9"/>
-        <v>4.6569647793637736E-3</v>
+        <v>5.9242232057697686E-4</v>
       </c>
       <c r="R46" s="9">
         <f t="shared" si="10"/>
-        <v>0.18107560852671845</v>
+        <v>0.81226174632110704</v>
       </c>
       <c r="S46" s="7"/>
       <c r="T46" s="7"/>
@@ -16590,31 +16653,31 @@
         <v>118</v>
       </c>
       <c r="D47" s="48">
-        <v>2.7542720000000003</v>
+        <v>2.8951366557581992</v>
       </c>
       <c r="E47" s="48">
-        <v>3.4524839999999992</v>
+        <v>3.6409690455151855</v>
       </c>
       <c r="F47" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G47" s="155"/>
-      <c r="H47" s="155"/>
+      <c r="G47" s="125"/>
+      <c r="H47" s="125"/>
       <c r="I47" s="55">
         <f t="shared" si="1"/>
-        <v>0.63559466883060201</v>
+        <v>0.75316139585195241</v>
       </c>
       <c r="J47" s="55">
         <f t="shared" si="2"/>
-        <v>2.1613359846690807</v>
+        <v>2.3318271604657981</v>
       </c>
       <c r="K47" s="56">
         <f t="shared" si="3"/>
-        <v>0.2302070334798634</v>
+        <v>0.17561105881568231</v>
       </c>
       <c r="L47" s="56">
         <f t="shared" si="4"/>
-        <v>3.3980685219654544E-37</v>
+        <v>3.8384561259920428E-37</v>
       </c>
       <c r="M47" s="56">
         <f t="shared" si="5"/>
@@ -16622,23 +16685,23 @@
       </c>
       <c r="N47" s="56">
         <f t="shared" si="6"/>
-        <v>2.1190278764349103E-37</v>
+        <v>2.4949106018779518E-37</v>
       </c>
       <c r="O47" s="57">
         <f t="shared" si="7"/>
-        <v>2.3142236695228603E-6</v>
+        <v>1.7653816340792731E-6</v>
       </c>
       <c r="P47" s="57">
         <f t="shared" si="8"/>
-        <v>3.3553769426649473E-4</v>
+        <v>3.7902317441012619E-4</v>
       </c>
       <c r="Q47" s="57">
         <f t="shared" si="9"/>
-        <v>6.5597808578110933E-3</v>
+        <v>7.7233843830707407E-3</v>
       </c>
       <c r="R47" s="9">
         <f t="shared" si="10"/>
-        <v>0.23142236695228602</v>
+        <v>0.1765381634079273</v>
       </c>
       <c r="S47" s="7"/>
       <c r="T47" s="7"/>
@@ -16663,50 +16726,57 @@
       <c r="C48" s="47" t="s">
         <v>120</v>
       </c>
-      <c r="D48" s="48"/>
-      <c r="E48" s="48"/>
+      <c r="D48" s="48">
+        <v>-1.7616394390778063</v>
+      </c>
+      <c r="E48" s="48">
+        <v>-2.9834589203782875</v>
+      </c>
       <c r="F48" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G48" s="155"/>
-      <c r="H48" s="155"/>
-      <c r="I48" s="83" t="str">
+      <c r="G48" s="125"/>
+      <c r="H48" s="125"/>
+      <c r="I48" s="83">
         <f t="shared" ref="I48:I50" si="11">IF(D48=0,"",LOG($K$15*10^D48+$K$16*10^E48+$K$14))</f>
-        <v/>
-      </c>
-      <c r="J48" s="83" t="str">
+        <v>-2.2481289635832413E-3</v>
+      </c>
+      <c r="J48" s="83">
         <f t="shared" ref="J48:J50" si="12">IF(D48=0,"",LOG($K$21*10^D48+$K$22*10^E48+$K$20))</f>
-        <v/>
-      </c>
-      <c r="K48" s="84" t="str">
+        <v>-5.7886483676924415E-2</v>
+      </c>
+      <c r="K48" s="84">
         <f t="shared" ref="K48:K50" si="13">IF(D48=0,"",1/(1+10^D48*$J$15/$J$14+10^E48*$J$16/$J$14+10^J48*$J$19/$J$14))</f>
-        <v/>
-      </c>
-      <c r="L48" s="84" t="str">
+        <v>0.99991109244463416</v>
+      </c>
+      <c r="L48" s="84">
         <f t="shared" ref="L48:L50" si="14">IF(D48=0,"",1/(1+10^I48/10^J48*$J$13/$J$19))</f>
-        <v/>
-      </c>
-      <c r="M48" s="84" t="str">
+        <v>8.9094821405150025E-39</v>
+      </c>
+      <c r="M48" s="84">
         <f t="shared" ref="M48:M92" si="15">IF(D48=0,"",1-L48)</f>
-        <v/>
-      </c>
-      <c r="N48" s="84" t="str">
+        <v>1</v>
+      </c>
+      <c r="N48" s="84">
         <f t="shared" ref="N48:N50" si="16">IF(D48=0,"",1/(1/10^E48*$J$20/$J$22+10^D48/10^E48*$J$21/$J$22+10^I48/10^E48*$J$13/$J$22+1))</f>
-        <v/>
-      </c>
-      <c r="O48" s="85" t="str">
+        <v>3.3731569378809204E-43</v>
+      </c>
+      <c r="O48" s="85">
         <f t="shared" ref="O48:O92" si="17">IF(D48=0,"",F48*K48*$J$7/$J$14)</f>
-        <v/>
-      </c>
-      <c r="P48" s="85" t="str">
+        <v>1.0051899295058874E-5</v>
+      </c>
+      <c r="P48" s="85">
         <f t="shared" ref="P48:P50" si="18">IF(D48=0,"",O48*10^J48)</f>
-        <v/>
-      </c>
-      <c r="Q48" s="85" t="str">
+        <v>8.7975480047347597E-6</v>
+      </c>
+      <c r="Q48" s="85">
         <f t="shared" ref="Q48:Q50" si="19">IF(D48=0,"",F48*N48*$J$7/$J$22)</f>
-        <v/>
-      </c>
-      <c r="R48" s="9"/>
+        <v>1.0442132714521474E-8</v>
+      </c>
+      <c r="R48" s="9">
+        <f t="shared" si="10"/>
+        <v>1.0051899295058873</v>
+      </c>
       <c r="S48" s="7"/>
       <c r="T48" s="7"/>
       <c r="U48" s="7"/>
@@ -16731,31 +16801,31 @@
         <v>122</v>
       </c>
       <c r="D49" s="48">
-        <v>2.3368320000000007</v>
+        <v>1.1365502998865107</v>
       </c>
       <c r="E49" s="48">
-        <v>2.6380540000000012</v>
+        <v>1.1393180322329237</v>
       </c>
       <c r="F49" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G49" s="155"/>
-      <c r="H49" s="155"/>
+      <c r="G49" s="125"/>
+      <c r="H49" s="125"/>
       <c r="I49" s="55">
         <f t="shared" si="11"/>
-        <v>0.33612090437875913</v>
+        <v>2.8034222802740122E-2</v>
       </c>
       <c r="J49" s="55">
         <f t="shared" si="12"/>
-        <v>1.5474327219604984</v>
+        <v>0.41632864919457246</v>
       </c>
       <c r="K49" s="56">
         <f t="shared" si="13"/>
-        <v>0.45876719243742409</v>
+        <v>0.9325648335686878</v>
       </c>
       <c r="L49" s="56">
         <f t="shared" si="14"/>
-        <v>1.6474135506111304E-37</v>
+        <v>2.4761972828795106E-38</v>
       </c>
       <c r="M49" s="56">
         <f t="shared" si="15"/>
@@ -16763,23 +16833,23 @@
       </c>
       <c r="N49" s="56">
         <f t="shared" si="16"/>
-        <v>6.4741153718466284E-38</v>
+        <v>4.1737953250596352E-39</v>
       </c>
       <c r="O49" s="57">
         <f t="shared" si="17"/>
-        <v>4.6118916502701203E-6</v>
+        <v>9.3748812909232103E-6</v>
       </c>
       <c r="P49" s="57">
         <f t="shared" si="18"/>
-        <v>1.6267162969265685E-4</v>
+        <v>2.4450876180854041E-5</v>
       </c>
       <c r="Q49" s="57">
         <f t="shared" si="19"/>
-        <v>2.00416325616963E-3</v>
+        <v>1.2920633551933653E-4</v>
       </c>
       <c r="R49" s="9">
         <f t="shared" si="10"/>
-        <v>0.46118916502701202</v>
+        <v>0.93748812909232093</v>
       </c>
       <c r="S49" s="7"/>
       <c r="T49" s="7"/>
@@ -16805,31 +16875,31 @@
         <v>124</v>
       </c>
       <c r="D50" s="48">
-        <v>9.5872000000000845E-2</v>
+        <v>-0.16497034264114602</v>
       </c>
       <c r="E50" s="48">
-        <v>7.4959000000001108E-2</v>
+        <v>-0.71214090995430623</v>
       </c>
       <c r="F50" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G50" s="155"/>
-      <c r="H50" s="155"/>
+      <c r="G50" s="125"/>
+      <c r="H50" s="125"/>
       <c r="I50" s="55">
         <f t="shared" si="11"/>
-        <v>5.5915337361630017E-4</v>
+        <v>-7.5375052843166363E-4</v>
       </c>
       <c r="J50" s="55">
         <f t="shared" si="12"/>
-        <v>1.2570261411322906E-2</v>
+        <v>-2.4841044273260518E-2</v>
       </c>
       <c r="K50" s="56">
         <f t="shared" si="13"/>
-        <v>0.99346850557649646</v>
+        <v>0.99647637756323659</v>
       </c>
       <c r="L50" s="56">
         <f t="shared" si="14"/>
-        <v>1.0411227208252657E-38</v>
+        <v>9.5808385674962699E-39</v>
       </c>
       <c r="M50" s="56">
         <f t="shared" si="15"/>
@@ -16837,23 +16907,23 @@
       </c>
       <c r="N50" s="56">
         <f t="shared" si="16"/>
-        <v>3.8339565388804123E-40</v>
+        <v>6.2785618874171645E-41</v>
       </c>
       <c r="O50" s="57">
         <f t="shared" si="17"/>
-        <v>9.9871333024746133E-6</v>
+        <v>1.0017370817121261E-5</v>
       </c>
       <c r="P50" s="57">
         <f t="shared" si="18"/>
-        <v>1.0280425922432904E-5</v>
+        <v>9.4604698560280717E-6</v>
       </c>
       <c r="Q50" s="57">
         <f t="shared" si="19"/>
-        <v>1.1868609654980122E-5</v>
+        <v>1.943626629063202E-6</v>
       </c>
       <c r="R50" s="9">
         <f t="shared" si="10"/>
-        <v>0.99871333024746123</v>
+        <v>1.0017370817121261</v>
       </c>
       <c r="S50" s="7"/>
       <c r="T50" s="7"/>
@@ -16878,50 +16948,57 @@
       <c r="C51" s="47" t="s">
         <v>126</v>
       </c>
-      <c r="D51" s="48"/>
-      <c r="E51" s="48"/>
+      <c r="D51" s="48">
+        <v>-2.7256879443499291</v>
+      </c>
+      <c r="E51" s="48">
+        <v>-4.3548518644977863</v>
+      </c>
       <c r="F51" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G51" s="155"/>
-      <c r="H51" s="155"/>
-      <c r="I51" s="55" t="str">
+      <c r="G51" s="125"/>
+      <c r="H51" s="125"/>
+      <c r="I51" s="55">
         <f t="shared" ref="I51:I70" si="20">IF(D51=0,"",LOG($K$15*10^D51+$K$16*10^E51+$K$14))</f>
-        <v/>
-      </c>
-      <c r="J51" s="55" t="str">
+        <v>-2.2825524935015497E-3</v>
+      </c>
+      <c r="J51" s="55">
         <f t="shared" ref="J51:J70" si="21">IF(D51=0,"",LOG($K$21*10^D51+$K$22*10^E51+$K$20))</f>
-        <v/>
-      </c>
-      <c r="K51" s="56" t="str">
+        <v>-5.8626956352040294E-2</v>
+      </c>
+      <c r="K51" s="56">
         <f t="shared" ref="K51:K70" si="22">IF(D51=0,"",1/(1+10^D51*$J$15/$J$14+10^E51*$J$16/$J$14+10^J51*$J$19/$J$14))</f>
-        <v/>
-      </c>
-      <c r="L51" s="56" t="str">
+        <v>0.9999903516455072</v>
+      </c>
+      <c r="L51" s="56">
         <f t="shared" ref="L51:L70" si="23">IF(D51=0,"",1/(1+10^I51/10^J51*$J$13/$J$19))</f>
-        <v/>
-      </c>
-      <c r="M51" s="56" t="str">
+        <v>8.8950094223436973E-39</v>
+      </c>
+      <c r="M51" s="56">
         <f t="shared" ref="M51:M70" si="24">IF(D51=0,"",1-L51)</f>
-        <v/>
-      </c>
-      <c r="N51" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N51" s="56">
         <f t="shared" ref="N51:N70" si="25">IF(D51=0,"",1/(1/10^E51*$J$20/$J$22+10^D51/10^E51*$J$21/$J$22+10^I51/10^E51*$J$13/$J$22+1))</f>
-        <v/>
-      </c>
-      <c r="O51" s="57" t="str">
+        <v>1.4344255981109346E-44</v>
+      </c>
+      <c r="O51" s="57">
         <f t="shared" ref="O51:O70" si="26">IF(D51=0,"",F51*K51*$J$7/$J$14)</f>
-        <v/>
-      </c>
-      <c r="P51" s="57" t="str">
+        <v>1.0052696071403694E-5</v>
+      </c>
+      <c r="P51" s="57">
         <f t="shared" ref="P51:P70" si="27">IF(D51=0,"",O51*10^J51)</f>
-        <v/>
-      </c>
-      <c r="Q51" s="57" t="str">
+        <v>8.7832571143257582E-6</v>
+      </c>
+      <c r="Q51" s="57">
         <f t="shared" ref="Q51:Q70" si="28">IF(D51=0,"",F51*N51*$J$7/$J$22)</f>
-        <v/>
-      </c>
-      <c r="R51" s="9"/>
+        <v>4.4404878695003647E-10</v>
+      </c>
+      <c r="R51" s="9">
+        <f t="shared" si="10"/>
+        <v>1.0052696071403693</v>
+      </c>
       <c r="S51" s="7"/>
       <c r="T51" s="7"/>
       <c r="U51" s="7"/>
@@ -16945,50 +17022,57 @@
       <c r="C52" s="47" t="s">
         <v>128</v>
       </c>
-      <c r="D52" s="48"/>
-      <c r="E52" s="48"/>
+      <c r="D52" s="48">
+        <v>-0.21545001227559774</v>
+      </c>
+      <c r="E52" s="48">
+        <v>-0.78395001746247006</v>
+      </c>
       <c r="F52" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G52" s="155"/>
-      <c r="H52" s="155"/>
-      <c r="I52" s="55" t="str">
+      <c r="G52" s="125"/>
+      <c r="H52" s="125"/>
+      <c r="I52" s="55">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="J52" s="55" t="str">
+        <v>-9.2225289384114328E-4</v>
+      </c>
+      <c r="J52" s="55">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="K52" s="56" t="str">
+        <v>-2.8554234727833281E-2</v>
+      </c>
+      <c r="K52" s="56">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="L52" s="56" t="str">
+        <v>0.99686307647705219</v>
+      </c>
+      <c r="L52" s="56">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="M52" s="56" t="str">
+        <v>9.5029585395557171E-39</v>
+      </c>
+      <c r="M52" s="56">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="N52" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N52" s="56">
         <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="O52" s="57" t="str">
+        <v>5.3237735508681026E-41</v>
+      </c>
+      <c r="O52" s="57">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="P52" s="57" t="str">
+        <v>1.0021258221280044E-5</v>
+      </c>
+      <c r="P52" s="57">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="Q52" s="57" t="str">
+        <v>9.3835682725677437E-6</v>
+      </c>
+      <c r="Q52" s="57">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="R52" s="9"/>
+        <v>1.6480570274073168E-6</v>
+      </c>
+      <c r="R52" s="9">
+        <f t="shared" si="10"/>
+        <v>1.0021258221280043</v>
+      </c>
       <c r="S52" s="7"/>
       <c r="T52" s="7"/>
       <c r="U52" s="7"/>
@@ -17021,8 +17105,8 @@
       <c r="F53" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G53" s="155"/>
-      <c r="H53" s="155"/>
+      <c r="G53" s="125"/>
+      <c r="H53" s="125"/>
       <c r="I53" s="55">
         <f t="shared" si="20"/>
         <v>2.1370520703130572E-2</v>
@@ -17087,31 +17171,31 @@
         <v>132</v>
       </c>
       <c r="D54" s="48">
-        <v>-0.1224400000000001</v>
+        <v>-1.8497486811018407</v>
       </c>
       <c r="E54" s="48">
-        <v>-0.24365499999999995</v>
+        <v>-3.1087974195955765</v>
       </c>
       <c r="F54" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G54" s="155"/>
-      <c r="H54" s="155"/>
+      <c r="G54" s="125"/>
+      <c r="H54" s="125"/>
       <c r="I54" s="55">
         <f t="shared" si="20"/>
-        <v>-5.7279857385541535E-4</v>
+        <v>-2.255223699802863E-3</v>
       </c>
       <c r="J54" s="55">
         <f t="shared" si="21"/>
-        <v>-1.6340820505326824E-2</v>
+        <v>-5.8039797695071449E-2</v>
       </c>
       <c r="K54" s="56">
         <f t="shared" si="22"/>
-        <v>0.99606127491677099</v>
+        <v>0.9999274273595028</v>
       </c>
       <c r="L54" s="56">
         <f t="shared" si="23"/>
-        <v>9.7661365971776656E-39</v>
+        <v>8.9064829801402721E-39</v>
       </c>
       <c r="M54" s="56">
         <f t="shared" si="24"/>
@@ -17119,23 +17203,23 @@
       </c>
       <c r="N54" s="56">
         <f t="shared" si="25"/>
-        <v>1.8457171067230343E-40</v>
+        <v>2.5275813542736579E-43</v>
       </c>
       <c r="O54" s="57">
         <f t="shared" si="26"/>
-        <v>1.0013197876115894E-5</v>
+        <v>1.0052063506577772E-5</v>
       </c>
       <c r="P54" s="57">
         <f t="shared" si="27"/>
-        <v>9.6434398968895741E-6</v>
+        <v>8.7945865242632285E-6</v>
       </c>
       <c r="Q54" s="57">
         <f t="shared" si="28"/>
-        <v>5.7137047984409271E-6</v>
+        <v>7.8245217860086406E-9</v>
       </c>
       <c r="R54" s="9">
         <f t="shared" si="10"/>
-        <v>1.0013197876115894</v>
+        <v>1.0052063506577771</v>
       </c>
       <c r="S54" s="7"/>
       <c r="T54" s="7"/>
@@ -17160,50 +17244,57 @@
       <c r="C55" s="47" t="s">
         <v>134</v>
       </c>
-      <c r="D55" s="48"/>
-      <c r="E55" s="48"/>
+      <c r="D55" s="48">
+        <v>-1.4544244920654867</v>
+      </c>
+      <c r="E55" s="48">
+        <v>-2.5464348408255515</v>
+      </c>
       <c r="F55" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G55" s="155"/>
-      <c r="H55" s="155"/>
-      <c r="I55" s="55" t="str">
+      <c r="G55" s="125"/>
+      <c r="H55" s="125"/>
+      <c r="I55" s="55">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="J55" s="55" t="str">
+        <v>-2.2083624388552618E-3</v>
+      </c>
+      <c r="J55" s="55">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="K55" s="56" t="str">
+        <v>-5.7023160665230277E-2</v>
+      </c>
+      <c r="K55" s="56">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="L55" s="56" t="str">
+        <v>0.99981953897013542</v>
+      </c>
+      <c r="L55" s="56">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="M55" s="56" t="str">
+        <v>8.9263933000278588E-39</v>
+      </c>
+      <c r="M55" s="56">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="N55" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N55" s="56">
         <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="O55" s="57" t="str">
+        <v>9.2261574208616936E-43</v>
+      </c>
+      <c r="O55" s="57">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="P55" s="57" t="str">
+        <v>1.0050978926925419E-5</v>
+      </c>
+      <c r="P55" s="57">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="Q55" s="57" t="str">
+        <v>8.814246701166681E-6</v>
+      </c>
+      <c r="Q55" s="57">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="R55" s="7"/>
+        <v>2.8561007390965923E-8</v>
+      </c>
+      <c r="R55" s="9">
+        <f t="shared" si="10"/>
+        <v>1.0050978926925418</v>
+      </c>
       <c r="S55" s="7"/>
       <c r="T55" s="7"/>
       <c r="U55" s="7"/>
@@ -17227,50 +17318,57 @@
       <c r="C56" s="47" t="s">
         <v>136</v>
       </c>
-      <c r="D56" s="48"/>
-      <c r="E56" s="48"/>
+      <c r="D56" s="48">
+        <v>2.3179513188981593</v>
+      </c>
+      <c r="E56" s="48">
+        <v>2.8199025804044244</v>
+      </c>
       <c r="F56" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G56" s="155"/>
-      <c r="H56" s="155"/>
-      <c r="I56" s="55" t="str">
+      <c r="G56" s="125"/>
+      <c r="H56" s="125"/>
+      <c r="I56" s="55">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="J56" s="55" t="str">
+        <v>0.33354419420746501</v>
+      </c>
+      <c r="J56" s="55">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="K56" s="56" t="str">
+        <v>1.6191635897655268</v>
+      </c>
+      <c r="K56" s="56">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="L56" s="56" t="str">
+        <v>0.46149719217602042</v>
+      </c>
+      <c r="L56" s="56">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="M56" s="56" t="str">
+        <v>1.9548354757879667E-37</v>
+      </c>
+      <c r="M56" s="56">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="N56" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N56" s="56">
         <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="O56" s="57" t="str">
+        <v>9.8993282469413863E-38</v>
+      </c>
+      <c r="O56" s="57">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="P56" s="57" t="str">
+        <v>4.6393357727078616E-6</v>
+      </c>
+      <c r="P56" s="57">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="Q56" s="57" t="str">
+        <v>1.9302759316838428E-4</v>
+      </c>
+      <c r="Q56" s="57">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="R56" s="7"/>
+        <v>3.0644912538256275E-3</v>
+      </c>
+      <c r="R56" s="9">
+        <f t="shared" si="10"/>
+        <v>0.4639335772707861</v>
+      </c>
       <c r="S56" s="7"/>
       <c r="T56" s="7"/>
       <c r="U56" s="7"/>
@@ -17294,50 +17392,57 @@
       <c r="C57" s="47" t="s">
         <v>138</v>
       </c>
-      <c r="D57" s="48"/>
-      <c r="E57" s="48"/>
+      <c r="D57" s="48">
+        <v>3.46</v>
+      </c>
+      <c r="E57" s="48">
+        <v>2.6247999825375303</v>
+      </c>
       <c r="F57" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G57" s="155"/>
-      <c r="H57" s="155"/>
-      <c r="I57" s="55" t="str">
+      <c r="G57" s="125"/>
+      <c r="H57" s="125"/>
+      <c r="I57" s="55">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="J57" s="55" t="str">
+        <v>1.1977426869383703</v>
+      </c>
+      <c r="J57" s="55">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="K57" s="56" t="str">
+        <v>2.4579318909163166</v>
+      </c>
+      <c r="K57" s="56">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="L57" s="56" t="str">
+        <v>6.30914589520431E-2</v>
+      </c>
+      <c r="L57" s="56">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="M57" s="56" t="str">
+        <v>1.8436565484675477E-37</v>
+      </c>
+      <c r="M57" s="56">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="N57" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N57" s="56">
         <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="O57" s="57" t="str">
+        <v>8.635840936127066E-39</v>
+      </c>
+      <c r="O57" s="57">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="P57" s="57" t="str">
+        <v>6.3424538097060211E-7</v>
+      </c>
+      <c r="P57" s="57">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="Q57" s="57" t="str">
+        <v>1.8204937990312081E-4</v>
+      </c>
+      <c r="Q57" s="57">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="R57" s="7"/>
+        <v>2.6733590762956553E-4</v>
+      </c>
+      <c r="R57" s="9">
+        <f t="shared" si="10"/>
+        <v>6.342453809706021E-2</v>
+      </c>
       <c r="S57" s="7"/>
       <c r="T57" s="7"/>
       <c r="U57" s="7"/>
@@ -17360,8 +17465,8 @@
       <c r="D58" s="48"/>
       <c r="E58" s="48"/>
       <c r="F58" s="58"/>
-      <c r="G58" s="155"/>
-      <c r="H58" s="155"/>
+      <c r="G58" s="125"/>
+      <c r="H58" s="125"/>
       <c r="I58" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17421,8 +17526,8 @@
       <c r="D59" s="48"/>
       <c r="E59" s="48"/>
       <c r="F59" s="58"/>
-      <c r="G59" s="155"/>
-      <c r="H59" s="155"/>
+      <c r="G59" s="125"/>
+      <c r="H59" s="125"/>
       <c r="I59" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17482,8 +17587,8 @@
       <c r="D60" s="48"/>
       <c r="E60" s="48"/>
       <c r="F60" s="58"/>
-      <c r="G60" s="155"/>
-      <c r="H60" s="155"/>
+      <c r="G60" s="125"/>
+      <c r="H60" s="125"/>
       <c r="I60" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17543,8 +17648,8 @@
       <c r="D61" s="48"/>
       <c r="E61" s="48"/>
       <c r="F61" s="58"/>
-      <c r="G61" s="155"/>
-      <c r="H61" s="155"/>
+      <c r="G61" s="125"/>
+      <c r="H61" s="125"/>
       <c r="I61" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17604,8 +17709,8 @@
       <c r="D62" s="48"/>
       <c r="E62" s="48"/>
       <c r="F62" s="58"/>
-      <c r="G62" s="155"/>
-      <c r="H62" s="155"/>
+      <c r="G62" s="125"/>
+      <c r="H62" s="125"/>
       <c r="I62" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17665,8 +17770,8 @@
       <c r="D63" s="48"/>
       <c r="E63" s="48"/>
       <c r="F63" s="58"/>
-      <c r="G63" s="155"/>
-      <c r="H63" s="155"/>
+      <c r="G63" s="125"/>
+      <c r="H63" s="125"/>
       <c r="I63" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17726,8 +17831,8 @@
       <c r="D64" s="48"/>
       <c r="E64" s="48"/>
       <c r="F64" s="58"/>
-      <c r="G64" s="155"/>
-      <c r="H64" s="155"/>
+      <c r="G64" s="125"/>
+      <c r="H64" s="125"/>
       <c r="I64" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17787,8 +17892,8 @@
       <c r="D65" s="48"/>
       <c r="E65" s="48"/>
       <c r="F65" s="58"/>
-      <c r="G65" s="155"/>
-      <c r="H65" s="155"/>
+      <c r="G65" s="125"/>
+      <c r="H65" s="125"/>
       <c r="I65" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17848,8 +17953,8 @@
       <c r="D66" s="48"/>
       <c r="E66" s="48"/>
       <c r="F66" s="58"/>
-      <c r="G66" s="155"/>
-      <c r="H66" s="155"/>
+      <c r="G66" s="125"/>
+      <c r="H66" s="125"/>
       <c r="I66" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17909,8 +18014,8 @@
       <c r="D67" s="48"/>
       <c r="E67" s="48"/>
       <c r="F67" s="58"/>
-      <c r="G67" s="155"/>
-      <c r="H67" s="155"/>
+      <c r="G67" s="125"/>
+      <c r="H67" s="125"/>
       <c r="I67" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17970,8 +18075,8 @@
       <c r="D68" s="48"/>
       <c r="E68" s="48"/>
       <c r="F68" s="58"/>
-      <c r="G68" s="155"/>
-      <c r="H68" s="155"/>
+      <c r="G68" s="125"/>
+      <c r="H68" s="125"/>
       <c r="I68" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -18031,8 +18136,8 @@
       <c r="D69" s="48"/>
       <c r="E69" s="48"/>
       <c r="F69" s="58"/>
-      <c r="G69" s="155"/>
-      <c r="H69" s="155"/>
+      <c r="G69" s="125"/>
+      <c r="H69" s="125"/>
       <c r="I69" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -18092,8 +18197,8 @@
       <c r="D70" s="48"/>
       <c r="E70" s="48"/>
       <c r="F70" s="58"/>
-      <c r="G70" s="155"/>
-      <c r="H70" s="155"/>
+      <c r="G70" s="125"/>
+      <c r="H70" s="125"/>
       <c r="I70" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -18153,8 +18258,8 @@
       <c r="D71" s="48"/>
       <c r="E71" s="48"/>
       <c r="F71" s="58"/>
-      <c r="G71" s="155"/>
-      <c r="H71" s="155"/>
+      <c r="G71" s="125"/>
+      <c r="H71" s="125"/>
       <c r="I71" s="55" t="str">
         <f t="shared" ref="I71:I122" si="29">IF(D71=0,"",LOG($K$15*10^D71+$K$16*10^E71+$K$14))</f>
         <v/>
@@ -18214,8 +18319,8 @@
       <c r="D72" s="48"/>
       <c r="E72" s="48"/>
       <c r="F72" s="58"/>
-      <c r="G72" s="155"/>
-      <c r="H72" s="155"/>
+      <c r="G72" s="125"/>
+      <c r="H72" s="125"/>
       <c r="I72" s="55" t="str">
         <f t="shared" si="29"/>
         <v/>
@@ -18275,8 +18380,8 @@
       <c r="D73" s="48"/>
       <c r="E73" s="48"/>
       <c r="F73" s="58"/>
-      <c r="G73" s="155"/>
-      <c r="H73" s="155"/>
+      <c r="G73" s="125"/>
+      <c r="H73" s="125"/>
       <c r="I73" s="55" t="str">
         <f t="shared" si="29"/>
         <v/>
@@ -18336,8 +18441,8 @@
       <c r="D74" s="48"/>
       <c r="E74" s="48"/>
       <c r="F74" s="58"/>
-      <c r="G74" s="155"/>
-      <c r="H74" s="155"/>
+      <c r="G74" s="125"/>
+      <c r="H74" s="125"/>
       <c r="I74" s="55" t="str">
         <f t="shared" si="29"/>
         <v/>
@@ -18397,8 +18502,8 @@
       <c r="D75" s="48"/>
       <c r="E75" s="48"/>
       <c r="F75" s="58"/>
-      <c r="G75" s="155"/>
-      <c r="H75" s="155"/>
+      <c r="G75" s="125"/>
+      <c r="H75" s="125"/>
       <c r="I75" s="55" t="str">
         <f t="shared" si="29"/>
         <v/>
@@ -18458,8 +18563,8 @@
       <c r="D76" s="48"/>
       <c r="E76" s="48"/>
       <c r="F76" s="58"/>
-      <c r="G76" s="155"/>
-      <c r="H76" s="155"/>
+      <c r="G76" s="125"/>
+      <c r="H76" s="125"/>
       <c r="I76" s="55" t="str">
         <f t="shared" si="29"/>
         <v/>
@@ -18519,8 +18624,8 @@
       <c r="D77" s="48"/>
       <c r="E77" s="48"/>
       <c r="F77" s="58"/>
-      <c r="G77" s="155"/>
-      <c r="H77" s="155"/>
+      <c r="G77" s="125"/>
+      <c r="H77" s="125"/>
       <c r="I77" s="55" t="str">
         <f t="shared" si="29"/>
         <v/>
@@ -25233,21 +25338,27 @@
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="L8:Q8"/>
-    <mergeCell ref="L9:Q9"/>
-    <mergeCell ref="P26:P27"/>
-    <mergeCell ref="I24:Q25"/>
-    <mergeCell ref="I23:Q23"/>
-    <mergeCell ref="Q26:Q27"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="J26:J27"/>
-    <mergeCell ref="O26:O27"/>
-    <mergeCell ref="K26:K27"/>
-    <mergeCell ref="L10:Q10"/>
-    <mergeCell ref="I11:Q11"/>
-    <mergeCell ref="L12:Q12"/>
-    <mergeCell ref="L13:Q13"/>
-    <mergeCell ref="M26:M27"/>
+    <mergeCell ref="I2:Q4"/>
+    <mergeCell ref="I5:Q5"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B8:F10"/>
+    <mergeCell ref="B11:F12"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="L19:Q19"/>
+    <mergeCell ref="L20:Q20"/>
+    <mergeCell ref="L21:Q21"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="L14:Q14"/>
     <mergeCell ref="L15:Q15"/>
@@ -25264,27 +25375,21 @@
     <mergeCell ref="I17:Q17"/>
     <mergeCell ref="B26:B27"/>
     <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="L19:Q19"/>
-    <mergeCell ref="L20:Q20"/>
-    <mergeCell ref="L21:Q21"/>
-    <mergeCell ref="I2:Q4"/>
-    <mergeCell ref="I5:Q5"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B8:F10"/>
-    <mergeCell ref="B11:F12"/>
+    <mergeCell ref="L8:Q8"/>
+    <mergeCell ref="L9:Q9"/>
+    <mergeCell ref="P26:P27"/>
+    <mergeCell ref="I24:Q25"/>
+    <mergeCell ref="I23:Q23"/>
+    <mergeCell ref="Q26:Q27"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="O26:O27"/>
+    <mergeCell ref="K26:K27"/>
+    <mergeCell ref="L10:Q10"/>
+    <mergeCell ref="I11:Q11"/>
+    <mergeCell ref="L12:Q12"/>
+    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="M26:M27"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
